--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260716.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260716.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,705,000</t>
+          <t>3,423,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>3,423,000</t>
+          <t>1,705,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>17,526,000</t>
+          <t>26,770,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>26,770,000</t>
+          <t>16,825,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>16,825,000</t>
+          <t>17,526,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>24,248,000</t>
+          <t>7,825,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,825,000</t>
+          <t>24,248,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
